--- a/SAP.xlsx
+++ b/SAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229C4C64-2C4B-41DB-8289-5E8BEF92138F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02314150-FA04-48B2-B148-210A195C8597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20800" yWindow="710" windowWidth="17600" windowHeight="20070" activeTab="1" xr2:uid="{32DCA01F-B437-43C4-8293-E13203F995C7}"/>
+    <workbookView xWindow="9060" yWindow="130" windowWidth="29080" windowHeight="15460" xr2:uid="{32DCA01F-B437-43C4-8293-E13203F995C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={B592C369-10A5-41EF-BD5D-A8AF76B1EFD6}</author>
+  </authors>
+  <commentList>
+    <comment ref="AV26" authorId="0" shapeId="0" xr:uid="{B592C369-10A5-41EF-BD5D-A8AF76B1EFD6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7.03 in USD</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
   <si>
     <t>Shares</t>
   </si>
@@ -252,13 +270,34 @@
   </si>
   <si>
     <t>Price EUR</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Christian Klein</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -277,6 +316,12 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -355,7 +400,7 @@
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>57910</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>9940</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -395,7 +440,63 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>50179</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>50179</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4AB81E-63FE-4040-AF5C-7BBC3F1DEE64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23351918" y="0"/>
+          <a:ext cx="0" cy="11290853"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Martin Shkreli" id="{08DB8A87-6DA9-47C6-AED0-631703363F5D}" userId="9ffda80931a57275" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,9 +794,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="AV26" dT="2026-01-20T14:41:17.24" personId="{08DB8A87-6DA9-47C6-AED0-631703363F5D}" id="{B592C369-10A5-41EF-BD5D-A8AF76B1EFD6}">
+    <text>7.03 in USD</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ACDACA0-F2A2-47B8-8EFC-1E2513D7ED69}">
-  <dimension ref="K2:M7"/>
+  <dimension ref="K2:M9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="6.453125" customWidth="1"/>
@@ -761,14 +870,22 @@
         <v>250472.39999999997</v>
       </c>
     </row>
+    <row r="9" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E87C550-93EA-49F8-8D50-E0A2F444052A}">
-  <dimension ref="A1:Z53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E87C550-93EA-49F8-8D50-E0A2F444052A}">
+  <dimension ref="A1:BF54"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -777,12 +894,12 @@
     <col min="5" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>48</v>
       </c>
@@ -858,8 +975,113 @@
       <c r="Z2" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2">
+        <v>2010</v>
+      </c>
+      <c r="AH2">
+        <v>2011</v>
+      </c>
+      <c r="AI2">
+        <v>2012</v>
+      </c>
+      <c r="AJ2">
+        <v>2013</v>
+      </c>
+      <c r="AK2">
+        <v>2014</v>
+      </c>
+      <c r="AL2">
+        <v>2015</v>
+      </c>
+      <c r="AM2">
+        <v>2016</v>
+      </c>
+      <c r="AN2">
+        <v>2017</v>
+      </c>
+      <c r="AO2">
+        <v>2018</v>
+      </c>
+      <c r="AP2">
+        <v>2019</v>
+      </c>
+      <c r="AQ2">
+        <v>2020</v>
+      </c>
+      <c r="AR2">
+        <f>+AQ2+1</f>
+        <v>2021</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" ref="AS2:BF2" si="0">+AR2+1</f>
+        <v>2022</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>2031</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>2032</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>2033</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="0"/>
+        <v>2034</v>
+      </c>
+      <c r="BF2">
+        <f t="shared" si="0"/>
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>62</v>
       </c>
@@ -891,7 +1113,7 @@
         <v>4586</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>63</v>
       </c>
@@ -910,7 +1132,7 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>47</v>
       </c>
@@ -929,7 +1151,7 @@
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -939,7 +1161,7 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
@@ -984,7 +1206,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
@@ -1011,7 +1233,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -1025,7 +1247,7 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1320,38 @@
       <c r="Y10" s="4">
         <v>5290</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z10" s="4">
+        <f>+V10*1.05</f>
+        <v>4943.4000000000005</v>
+      </c>
+      <c r="AP10" s="4">
+        <v>7013</v>
+      </c>
+      <c r="AQ10" s="4">
+        <v>8241</v>
+      </c>
+      <c r="AR10" s="4">
+        <f>SUM(G10:J10)</f>
+        <v>9418.4</v>
+      </c>
+      <c r="AS10" s="4">
+        <f>SUM(K10:N10)</f>
+        <v>11680</v>
+      </c>
+      <c r="AT10" s="4">
+        <f>SUM(O10:R10)</f>
+        <v>13665</v>
+      </c>
+      <c r="AU10" s="4">
+        <f>SUM(S10:V10)</f>
+        <v>17140</v>
+      </c>
+      <c r="AV10" s="4">
+        <f>SUM(W10:Z10)</f>
+        <v>20356.400000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1166,8 +1418,38 @@
       <c r="Y11" s="4">
         <v>161</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z11" s="4">
+        <f>+V11*1.05</f>
+        <v>717.15</v>
+      </c>
+      <c r="AP11" s="4">
+        <v>4533</v>
+      </c>
+      <c r="AQ11" s="4">
+        <v>3770</v>
+      </c>
+      <c r="AR11" s="4">
+        <f>SUM(G11:J11)</f>
+        <v>3248</v>
+      </c>
+      <c r="AS11" s="4">
+        <f>SUM(K11:N11)</f>
+        <v>2056</v>
+      </c>
+      <c r="AT11" s="4">
+        <f>SUM(O11:R11)</f>
+        <v>1768</v>
+      </c>
+      <c r="AU11" s="4">
+        <f>SUM(S11:V11)</f>
+        <v>1400</v>
+      </c>
+      <c r="AV11" s="4">
+        <f>SUM(W11:Z11)</f>
+        <v>1255.1500000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>22</v>
       </c>
@@ -1234,8 +1516,38 @@
       <c r="Y12" s="4">
         <v>2565</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z12" s="4">
+        <f>+V12*1.05</f>
+        <v>3019.8</v>
+      </c>
+      <c r="AP12" s="4">
+        <v>11548</v>
+      </c>
+      <c r="AQ12" s="4">
+        <v>11712</v>
+      </c>
+      <c r="AR12" s="4">
+        <f>SUM(G12:J12)</f>
+        <v>11411.4</v>
+      </c>
+      <c r="AS12" s="4">
+        <f>SUM(K12:N12)</f>
+        <v>11909</v>
+      </c>
+      <c r="AT12" s="4">
+        <f>SUM(O12:R12)</f>
+        <v>11496</v>
+      </c>
+      <c r="AU12" s="4">
+        <f>SUM(S12:V12)</f>
+        <v>11290</v>
+      </c>
+      <c r="AV12" s="4">
+        <f>SUM(W12:Z12)</f>
+        <v>10987.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
@@ -1248,8 +1560,14 @@
       <c r="G13" s="5">
         <v>919</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="H13" s="5">
+        <f>+G13</f>
+        <v>919</v>
+      </c>
+      <c r="I13" s="5">
+        <f>+H13</f>
+        <v>919</v>
+      </c>
       <c r="J13" s="5">
         <v>991</v>
       </c>
@@ -1298,8 +1616,38 @@
       <c r="Y13" s="4">
         <v>1060</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="Z13" s="4">
+        <f>+V13*1.05</f>
+        <v>1165.5</v>
+      </c>
+      <c r="AP13" s="4">
+        <v>4541</v>
+      </c>
+      <c r="AQ13" s="4">
+        <v>4174</v>
+      </c>
+      <c r="AR13" s="4">
+        <f>SUM(G13:J13)</f>
+        <v>3748</v>
+      </c>
+      <c r="AS13" s="4">
+        <f>SUM(K13:N13)</f>
+        <v>4178</v>
+      </c>
+      <c r="AT13" s="4">
+        <f>SUM(O13:R13)</f>
+        <v>4278</v>
+      </c>
+      <c r="AU13" s="4">
+        <f>SUM(S13:V13)</f>
+        <v>4346</v>
+      </c>
+      <c r="AV13" s="4">
+        <f>SUM(W13:Z13)</f>
+        <v>4361.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58" s="7" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>6</v>
       </c>
@@ -1329,15 +1677,15 @@
         <v>7077</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" ref="L14:N14" si="0">SUM(L10:L13)</f>
+        <f t="shared" ref="L14:N14" si="1">SUM(L10:L13)</f>
         <v>7206</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7477</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8063</v>
       </c>
       <c r="O14" s="8">
@@ -1345,51 +1693,97 @@
         <v>7442</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" ref="P14:Z14" si="1">SUM(P10:P13)</f>
+        <f t="shared" ref="P14:Z14" si="2">SUM(P10:P13)</f>
         <v>7554</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7744</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8467</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8041</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8288</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8470</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9377</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9012</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9027</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9076</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>9845.85</v>
+      </c>
+      <c r="AL14" s="7">
+        <v>22062</v>
+      </c>
+      <c r="AM14" s="7">
+        <v>23461</v>
+      </c>
+      <c r="AN14" s="7">
+        <v>24708</v>
+      </c>
+      <c r="AO14" s="7">
+        <v>27553</v>
+      </c>
+      <c r="AP14" s="7">
+        <f t="shared" ref="AP14:AQ14" si="3">SUM(AP10:AP13)</f>
+        <v>27635</v>
+      </c>
+      <c r="AQ14" s="7">
+        <f t="shared" si="3"/>
+        <v>27897</v>
+      </c>
+      <c r="AR14" s="7">
+        <f>SUM(AR10:AR13)</f>
+        <v>27825.8</v>
+      </c>
+      <c r="AS14" s="7">
+        <f>SUM(AS10:AS13)</f>
+        <v>29823</v>
+      </c>
+      <c r="AT14" s="7">
+        <f>SUM(AT10:AT13)</f>
+        <v>31207</v>
+      </c>
+      <c r="AU14" s="7">
+        <f>SUM(AU10:AU13)</f>
+        <v>34176</v>
+      </c>
+      <c r="AV14" s="7">
+        <f>SUM(AV10:AV13)</f>
+        <v>36960.850000000006</v>
+      </c>
+      <c r="AW14" s="7">
+        <v>40760</v>
+      </c>
+      <c r="AX14" s="7">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1403,8 +1797,14 @@
       <c r="G15" s="5">
         <v>1884</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="H15" s="5">
+        <f>+H14*0.25</f>
+        <v>1667.25</v>
+      </c>
+      <c r="I15" s="5">
+        <f>+I14*0.25</f>
+        <v>1711.25</v>
+      </c>
       <c r="J15" s="5">
         <f>873+531.2+753.2</f>
         <v>2157.4</v>
@@ -1460,8 +1860,42 @@
       <c r="Y15" s="4">
         <v>2405</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP15" s="4">
+        <v>7655</v>
+      </c>
+      <c r="AQ15" s="4">
+        <v>7362</v>
+      </c>
+      <c r="AR15" s="4">
+        <f>SUM(G15:J15)</f>
+        <v>7419.9</v>
+      </c>
+      <c r="AS15" s="4">
+        <f>SUM(K15:N15)</f>
+        <v>8252</v>
+      </c>
+      <c r="AT15" s="4">
+        <f>SUM(O15:R15)</f>
+        <v>8680</v>
+      </c>
+      <c r="AU15" s="4">
+        <f>SUM(S15:V15)</f>
+        <v>9243</v>
+      </c>
+      <c r="AV15" s="4">
+        <f>+AV14-AV16</f>
+        <v>9979.429500000002</v>
+      </c>
+      <c r="AW15" s="4">
+        <f>+AW14-AW16</f>
+        <v>11005.2</v>
+      </c>
+      <c r="AX15" s="4">
+        <f>+AX14-AX16</f>
+        <v>12395.700000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1477,19 +1911,19 @@
         <v>4464</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" ref="H16:K16" si="2">H14-H15</f>
-        <v>6669</v>
+        <f t="shared" ref="H16:K16" si="4">H14-H15</f>
+        <v>5001.75</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="2"/>
-        <v>6845</v>
+        <f t="shared" si="4"/>
+        <v>5133.75</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5823.4</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4978</v>
       </c>
       <c r="L16" s="5">
@@ -1501,31 +1935,31 @@
         <v>5440</v>
       </c>
       <c r="N16" s="4">
-        <f t="shared" ref="N16" si="3">+N14-N15</f>
+        <f t="shared" ref="N16" si="5">+N14-N15</f>
         <v>5914</v>
       </c>
       <c r="O16" s="4">
-        <f t="shared" ref="O16:T16" si="4">+O14-O15</f>
+        <f t="shared" ref="O16:T16" si="6">+O14-O15</f>
         <v>5286</v>
       </c>
       <c r="P16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5409</v>
       </c>
       <c r="Q16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5636</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6196</v>
       </c>
       <c r="S16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5762</v>
       </c>
       <c r="T16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6017</v>
       </c>
       <c r="U16" s="4">
@@ -1548,8 +1982,44 @@
         <f>+Y14-Y15</f>
         <v>6671</v>
       </c>
-    </row>
-    <row r="17" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP16" s="4">
+        <f t="shared" ref="AP16:AQ16" si="7">+AP14-AP15</f>
+        <v>19980</v>
+      </c>
+      <c r="AQ16" s="4">
+        <f t="shared" si="7"/>
+        <v>20535</v>
+      </c>
+      <c r="AR16" s="4">
+        <f>+AR14-AR15</f>
+        <v>20405.900000000001</v>
+      </c>
+      <c r="AS16" s="4">
+        <f t="shared" ref="AS16:AU16" si="8">+AS14-AS15</f>
+        <v>21571</v>
+      </c>
+      <c r="AT16" s="4">
+        <f t="shared" si="8"/>
+        <v>22527</v>
+      </c>
+      <c r="AU16" s="4">
+        <f t="shared" si="8"/>
+        <v>24933</v>
+      </c>
+      <c r="AV16" s="4">
+        <f>+AV14*0.73</f>
+        <v>26981.420500000004</v>
+      </c>
+      <c r="AW16" s="4">
+        <f>+AW14*0.73</f>
+        <v>29754.799999999999</v>
+      </c>
+      <c r="AX16" s="4">
+        <f>+AX14*0.73</f>
+        <v>33514.299999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1562,8 +2032,14 @@
       <c r="G17" s="5">
         <v>1171</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="H17" s="5">
+        <f>+G17</f>
+        <v>1171</v>
+      </c>
+      <c r="I17" s="5">
+        <f>+H17</f>
+        <v>1171</v>
+      </c>
       <c r="J17" s="5">
         <v>1412</v>
       </c>
@@ -1612,8 +2088,42 @@
       <c r="Y17" s="4">
         <v>1644</v>
       </c>
-    </row>
-    <row r="18" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP17" s="4">
+        <v>3854</v>
+      </c>
+      <c r="AQ17" s="4">
+        <v>4151</v>
+      </c>
+      <c r="AR17" s="4">
+        <f>SUM(G17:J17)</f>
+        <v>4925</v>
+      </c>
+      <c r="AS17" s="4">
+        <f>SUM(K17:N17)</f>
+        <v>6108</v>
+      </c>
+      <c r="AT17" s="4">
+        <f>SUM(O17:R17)</f>
+        <v>6322</v>
+      </c>
+      <c r="AU17" s="4">
+        <f>SUM(S17:V17)</f>
+        <v>6513</v>
+      </c>
+      <c r="AV17" s="4">
+        <f>+AU17</f>
+        <v>6513</v>
+      </c>
+      <c r="AW17" s="4">
+        <f t="shared" ref="AW17:AX17" si="9">+AV17</f>
+        <v>6513</v>
+      </c>
+      <c r="AX17" s="4">
+        <f t="shared" si="9"/>
+        <v>6513</v>
+      </c>
+    </row>
+    <row r="18" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>28</v>
       </c>
@@ -1626,8 +2136,14 @@
       <c r="G18" s="5">
         <v>1663</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="H18" s="5">
+        <f t="shared" ref="H18:I18" si="10">+G18</f>
+        <v>1663</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="10"/>
+        <v>1663</v>
+      </c>
       <c r="J18" s="5">
         <v>2168</v>
       </c>
@@ -1676,8 +2192,42 @@
       <c r="Y18" s="4">
         <v>2185</v>
       </c>
-    </row>
-    <row r="19" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP18" s="4">
+        <v>6784</v>
+      </c>
+      <c r="AQ18" s="4">
+        <v>6371</v>
+      </c>
+      <c r="AR18" s="4">
+        <f>SUM(G18:J18)</f>
+        <v>7157</v>
+      </c>
+      <c r="AS18" s="4">
+        <f>SUM(K18:N18)</f>
+        <v>8191</v>
+      </c>
+      <c r="AT18" s="4">
+        <f>SUM(O18:R18)</f>
+        <v>8828</v>
+      </c>
+      <c r="AU18" s="4">
+        <f>SUM(S18:V18)</f>
+        <v>9089</v>
+      </c>
+      <c r="AV18" s="4">
+        <f t="shared" ref="AV18:AX18" si="11">+AU18</f>
+        <v>9089</v>
+      </c>
+      <c r="AW18" s="4">
+        <f t="shared" si="11"/>
+        <v>9089</v>
+      </c>
+      <c r="AX18" s="4">
+        <f t="shared" si="11"/>
+        <v>9089</v>
+      </c>
+    </row>
+    <row r="19" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
@@ -1690,8 +2240,14 @@
       <c r="G19" s="5">
         <v>505</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="H19" s="5">
+        <f t="shared" ref="H19:I19" si="12">+G19</f>
+        <v>505</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="12"/>
+        <v>505</v>
+      </c>
       <c r="J19" s="5">
         <v>756</v>
       </c>
@@ -1740,8 +2296,42 @@
       <c r="Y19" s="4">
         <v>364</v>
       </c>
-    </row>
-    <row r="20" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP19" s="4">
+        <v>1152</v>
+      </c>
+      <c r="AQ19" s="4">
+        <v>1190</v>
+      </c>
+      <c r="AR19" s="4">
+        <f>SUM(G19:J19)</f>
+        <v>2271</v>
+      </c>
+      <c r="AS19" s="4">
+        <f>SUM(K19:N19)</f>
+        <v>1523</v>
+      </c>
+      <c r="AT19" s="4">
+        <f>SUM(O19:R19)</f>
+        <v>1359</v>
+      </c>
+      <c r="AU19" s="4">
+        <f>SUM(S19:V19)</f>
+        <v>1435</v>
+      </c>
+      <c r="AV19" s="4">
+        <f t="shared" ref="AV19:AX19" si="13">+AU19</f>
+        <v>1435</v>
+      </c>
+      <c r="AW19" s="4">
+        <f t="shared" si="13"/>
+        <v>1435</v>
+      </c>
+      <c r="AX19" s="4">
+        <f t="shared" si="13"/>
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="20" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
@@ -1749,7 +2339,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5">
-        <f t="shared" ref="F20" si="5">SUM(F17:F19)</f>
+        <f t="shared" ref="F20" si="14">SUM(F17:F19)</f>
         <v>3158</v>
       </c>
       <c r="G20" s="5">
@@ -1757,79 +2347,134 @@
         <v>3339</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" ref="H20:K20" si="6">SUM(H17:H19)</f>
+        <f t="shared" ref="H20:K20" si="15">SUM(H17:H19)</f>
+        <v>3339</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="15"/>
+        <v>3339</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="15"/>
+        <v>4336</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="15"/>
+        <v>3916</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" ref="L20:M20" si="16">SUM(L17:L19)</f>
+        <v>3955</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" si="16"/>
+        <v>3901</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" ref="N20:O20" si="17">SUM(N17:N19)</f>
+        <v>4050</v>
+      </c>
+      <c r="O20" s="5">
+        <f t="shared" si="17"/>
+        <v>4212</v>
+      </c>
+      <c r="P20" s="5">
+        <f t="shared" ref="P20:T20" si="18">SUM(P17:P19)</f>
+        <v>4052</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="18"/>
+        <v>3947</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="18"/>
+        <v>4298</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="18"/>
+        <v>4303</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" si="18"/>
+        <v>4158</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" ref="U20:Y20" si="19">SUM(U17:U19)</f>
+        <v>4027</v>
+      </c>
+      <c r="V20" s="5">
+        <f t="shared" si="19"/>
+        <v>4549</v>
+      </c>
+      <c r="W20" s="5">
+        <f t="shared" si="19"/>
+        <v>4266</v>
+      </c>
+      <c r="X20" s="5">
+        <f t="shared" si="19"/>
+        <v>4135</v>
+      </c>
+      <c r="Y20" s="5">
+        <f t="shared" si="19"/>
+        <v>4193</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" ref="Z20:AX20" si="20">SUM(Z17:Z19)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <f t="shared" si="6"/>
-        <v>4336</v>
-      </c>
-      <c r="K20" s="5">
-        <f t="shared" si="6"/>
-        <v>3916</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" ref="L20:M20" si="7">SUM(L17:L19)</f>
-        <v>3955</v>
-      </c>
-      <c r="M20" s="5">
-        <f t="shared" si="7"/>
-        <v>3901</v>
-      </c>
-      <c r="N20" s="5">
-        <f t="shared" ref="N20:O20" si="8">SUM(N17:N19)</f>
-        <v>4050</v>
-      </c>
-      <c r="O20" s="5">
-        <f t="shared" si="8"/>
-        <v>4212</v>
-      </c>
-      <c r="P20" s="5">
-        <f t="shared" ref="P20:T20" si="9">SUM(P17:P19)</f>
-        <v>4052</v>
-      </c>
-      <c r="Q20" s="5">
-        <f t="shared" si="9"/>
-        <v>3947</v>
-      </c>
-      <c r="R20" s="5">
-        <f t="shared" si="9"/>
-        <v>4298</v>
-      </c>
-      <c r="S20" s="5">
-        <f t="shared" si="9"/>
-        <v>4303</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" si="9"/>
-        <v>4158</v>
-      </c>
-      <c r="U20" s="5">
-        <f t="shared" ref="U20:Y20" si="10">SUM(U17:U19)</f>
-        <v>4027</v>
-      </c>
-      <c r="V20" s="5">
-        <f t="shared" si="10"/>
-        <v>4549</v>
-      </c>
-      <c r="W20" s="5">
-        <f t="shared" si="10"/>
-        <v>4266</v>
-      </c>
-      <c r="X20" s="5">
-        <f t="shared" si="10"/>
-        <v>4135</v>
-      </c>
-      <c r="Y20" s="5">
-        <f t="shared" si="10"/>
-        <v>4193</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="5"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="5"/>
+      <c r="AP20" s="5">
+        <f t="shared" ref="AP20:AR20" si="21">SUM(AP17:AP19)</f>
+        <v>11790</v>
+      </c>
+      <c r="AQ20" s="5">
+        <f t="shared" si="21"/>
+        <v>11712</v>
+      </c>
+      <c r="AR20" s="5">
+        <f t="shared" si="20"/>
+        <v>14353</v>
+      </c>
+      <c r="AS20" s="5">
+        <f t="shared" si="20"/>
+        <v>15822</v>
+      </c>
+      <c r="AT20" s="5">
+        <f t="shared" si="20"/>
+        <v>16509</v>
+      </c>
+      <c r="AU20" s="5">
+        <f t="shared" si="20"/>
+        <v>17037</v>
+      </c>
+      <c r="AV20" s="5">
+        <f t="shared" si="20"/>
+        <v>17037</v>
+      </c>
+      <c r="AW20" s="5">
+        <f t="shared" si="20"/>
+        <v>17037</v>
+      </c>
+      <c r="AX20" s="5">
+        <f t="shared" si="20"/>
+        <v>17037</v>
+      </c>
+    </row>
+    <row r="21" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>31</v>
       </c>
@@ -1837,7 +2482,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5">
-        <f t="shared" ref="F21" si="11">F16-F20</f>
+        <f t="shared" ref="F21" si="22">F16-F20</f>
         <v>2479</v>
       </c>
       <c r="G21" s="5">
@@ -1845,79 +2490,134 @@
         <v>1125</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" ref="H21:K21" si="12">H16-H20</f>
-        <v>6669</v>
+        <f t="shared" ref="H21:K21" si="23">H16-H20</f>
+        <v>1662.75</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="12"/>
-        <v>6845</v>
+        <f t="shared" si="23"/>
+        <v>1794.75</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1487.3999999999996</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="23"/>
         <v>1062</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" ref="L21:M21" si="13">L16-L20</f>
+        <f t="shared" ref="L21:M21" si="24">L16-L20</f>
         <v>1284</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="24"/>
         <v>1539</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" ref="N21:O21" si="14">N16-N20</f>
+        <f t="shared" ref="N21:O21" si="25">N16-N20</f>
         <v>1864</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>1074</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" ref="P21:T21" si="15">P16-P20</f>
+        <f t="shared" ref="P21:T21" si="26">P16-P20</f>
         <v>1357</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>1689</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>1898</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>1459</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>1859</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" ref="U21:Y21" si="16">U16-U20</f>
+        <f t="shared" ref="U21:Y21" si="27">U16-U20</f>
         <v>2185</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>2393</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>2340</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>2485</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="27"/>
         <v>2478</v>
       </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z21" s="5">
+        <f t="shared" ref="Z21:AV21" si="28">Z16-Z20</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="5"/>
+      <c r="AP21" s="5">
+        <f t="shared" ref="AP21:AR21" si="29">AP16-AP20</f>
+        <v>8190</v>
+      </c>
+      <c r="AQ21" s="5">
+        <f t="shared" si="29"/>
+        <v>8823</v>
+      </c>
+      <c r="AR21" s="5">
+        <f t="shared" si="28"/>
+        <v>6052.9000000000015</v>
+      </c>
+      <c r="AS21" s="5">
+        <f t="shared" si="28"/>
+        <v>5749</v>
+      </c>
+      <c r="AT21" s="5">
+        <f t="shared" si="28"/>
+        <v>6018</v>
+      </c>
+      <c r="AU21" s="5">
+        <f t="shared" si="28"/>
+        <v>7896</v>
+      </c>
+      <c r="AV21" s="5">
+        <f t="shared" si="28"/>
+        <v>9944.4205000000038</v>
+      </c>
+      <c r="AW21" s="5">
+        <f t="shared" ref="AW21:AX21" si="30">AW16-AW20</f>
+        <v>12717.8</v>
+      </c>
+      <c r="AX21" s="5">
+        <f t="shared" si="30"/>
+        <v>16477.299999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>33</v>
       </c>
@@ -1925,6 +2625,14 @@
         <v>107</v>
       </c>
       <c r="G22" s="2">
+        <v>315</v>
+      </c>
+      <c r="H22" s="2">
+        <f>+G22</f>
+        <v>315</v>
+      </c>
+      <c r="I22" s="2">
+        <f>+H22</f>
         <v>315</v>
       </c>
       <c r="J22" s="2">
@@ -1982,8 +2690,42 @@
       <c r="Y22" s="4">
         <v>212</v>
       </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="AP22" s="4">
+        <v>198</v>
+      </c>
+      <c r="AQ22" s="4">
+        <v>776</v>
+      </c>
+      <c r="AR22" s="4">
+        <f>SUM(G22:J22)</f>
+        <v>1468</v>
+      </c>
+      <c r="AS22" s="4">
+        <f>SUM(K22:N22)</f>
+        <v>-1476</v>
+      </c>
+      <c r="AT22" s="4">
+        <f>SUM(O22:R22)</f>
+        <v>-483</v>
+      </c>
+      <c r="AU22" s="4">
+        <f>SUM(S22:V22)</f>
+        <v>393</v>
+      </c>
+      <c r="AV22" s="4">
+        <f>+AU22</f>
+        <v>393</v>
+      </c>
+      <c r="AW22" s="4">
+        <f t="shared" ref="AW22:AX22" si="31">+AV22</f>
+        <v>393</v>
+      </c>
+      <c r="AX22" s="4">
+        <f t="shared" si="31"/>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="23" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>34</v>
       </c>
@@ -1996,79 +2738,119 @@
         <v>1440</v>
       </c>
       <c r="H23" s="5">
-        <f t="shared" ref="H23:K23" si="17">H21+H22</f>
-        <v>6669</v>
+        <f t="shared" ref="H23:K23" si="32">H21+H22</f>
+        <v>1977.75</v>
       </c>
       <c r="I23" s="5">
-        <f t="shared" si="17"/>
-        <v>6845</v>
+        <f t="shared" si="32"/>
+        <v>2109.75</v>
       </c>
       <c r="J23" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>2010.3999999999996</v>
       </c>
       <c r="K23" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>1006</v>
       </c>
       <c r="L23" s="4">
-        <f t="shared" ref="L23:N23" si="18">+L21+L22</f>
+        <f t="shared" ref="L23:N23" si="33">+L21+L22</f>
         <v>1071</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>1216</v>
       </c>
       <c r="N23" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>980</v>
       </c>
       <c r="O23" s="4">
-        <f t="shared" ref="O23:Y23" si="19">+O21+O22</f>
+        <f t="shared" ref="O23:Z23" si="34">+O21+O22</f>
         <v>954</v>
       </c>
       <c r="P23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>1182</v>
       </c>
       <c r="Q23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>1612</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>1787</v>
       </c>
       <c r="S23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>1410</v>
       </c>
       <c r="T23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2029</v>
       </c>
       <c r="U23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2184</v>
       </c>
       <c r="V23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2666</v>
       </c>
       <c r="W23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2465</v>
       </c>
       <c r="X23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2534</v>
       </c>
       <c r="Y23" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>2690</v>
       </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z23" s="4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="4">
+        <f t="shared" ref="AP23:AV23" si="35">+AP21+AP22</f>
+        <v>8388</v>
+      </c>
+      <c r="AQ23" s="4">
+        <f t="shared" si="35"/>
+        <v>9599</v>
+      </c>
+      <c r="AR23" s="4">
+        <f t="shared" si="35"/>
+        <v>7520.9000000000015</v>
+      </c>
+      <c r="AS23" s="4">
+        <f t="shared" si="35"/>
+        <v>4273</v>
+      </c>
+      <c r="AT23" s="4">
+        <f t="shared" si="35"/>
+        <v>5535</v>
+      </c>
+      <c r="AU23" s="4">
+        <f t="shared" si="35"/>
+        <v>8289</v>
+      </c>
+      <c r="AV23" s="4">
+        <f t="shared" si="35"/>
+        <v>10337.420500000004</v>
+      </c>
+      <c r="AW23" s="4">
+        <f t="shared" ref="AW23:AX23" si="36">+AW21+AW22</f>
+        <v>13110.8</v>
+      </c>
+      <c r="AX23" s="4">
+        <f t="shared" si="36"/>
+        <v>16870.299999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>37</v>
       </c>
@@ -2078,8 +2860,14 @@
       <c r="G24" s="5">
         <v>267</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="H24" s="5">
+        <f>+G24</f>
+        <v>267</v>
+      </c>
+      <c r="I24" s="5">
+        <f>+H24</f>
+        <v>267</v>
+      </c>
       <c r="J24" s="5">
         <v>513</v>
       </c>
@@ -2137,8 +2925,42 @@
       <c r="Y24">
         <v>694</v>
       </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="AP24" s="4">
+        <v>2180</v>
+      </c>
+      <c r="AQ24" s="4">
+        <v>2350</v>
+      </c>
+      <c r="AR24" s="4">
+        <f>SUM(G24:J24)</f>
+        <v>1314</v>
+      </c>
+      <c r="AS24" s="4">
+        <f>SUM(K24:N24)</f>
+        <v>1208</v>
+      </c>
+      <c r="AT24" s="4">
+        <f>SUM(O24:R24)</f>
+        <v>1694</v>
+      </c>
+      <c r="AU24" s="4">
+        <f>SUM(S24:V24)</f>
+        <v>1961</v>
+      </c>
+      <c r="AV24" s="4">
+        <f>+AV23*0.2</f>
+        <v>2067.484100000001</v>
+      </c>
+      <c r="AW24" s="4">
+        <f>+AW23*0.2</f>
+        <v>2622.16</v>
+      </c>
+      <c r="AX24" s="4">
+        <f>+AX23*0.2</f>
+        <v>3374.0599999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>35</v>
       </c>
@@ -2151,79 +2973,119 @@
         <v>1173</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:K25" si="20">H23-H24</f>
-        <v>6669</v>
+        <f t="shared" ref="H25:K25" si="37">H23-H24</f>
+        <v>1710.75</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="20"/>
-        <v>6845</v>
+        <f t="shared" si="37"/>
+        <v>1842.75</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>1497.3999999999996</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>693</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" ref="L25:N25" si="21">+L23-L24</f>
+        <f t="shared" ref="L25:N25" si="38">+L23-L24</f>
         <v>774</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v>926</v>
       </c>
       <c r="N25" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v>672</v>
       </c>
       <c r="O25" s="4">
-        <f t="shared" ref="O25:Y25" si="22">+O23-O24</f>
+        <f t="shared" ref="O25:Z25" si="39">+O23-O24</f>
         <v>683</v>
       </c>
       <c r="P25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>817</v>
       </c>
       <c r="Q25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1129</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1212</v>
       </c>
       <c r="S25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1249</v>
       </c>
       <c r="T25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1530</v>
       </c>
       <c r="U25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1474</v>
       </c>
       <c r="V25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>2075</v>
       </c>
       <c r="W25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1793</v>
       </c>
       <c r="X25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1781</v>
       </c>
       <c r="Y25" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>1996</v>
       </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="Z25" s="4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="4">
+        <f t="shared" ref="AP25:AX25" si="40">+AP23-AP24</f>
+        <v>6208</v>
+      </c>
+      <c r="AQ25" s="4">
+        <f t="shared" si="40"/>
+        <v>7249</v>
+      </c>
+      <c r="AR25" s="4">
+        <f t="shared" si="40"/>
+        <v>6206.9000000000015</v>
+      </c>
+      <c r="AS25" s="4">
+        <f t="shared" si="40"/>
+        <v>3065</v>
+      </c>
+      <c r="AT25" s="4">
+        <f t="shared" si="40"/>
+        <v>3841</v>
+      </c>
+      <c r="AU25" s="4">
+        <f t="shared" si="40"/>
+        <v>6328</v>
+      </c>
+      <c r="AV25" s="4">
+        <f t="shared" si="40"/>
+        <v>8269.9364000000023</v>
+      </c>
+      <c r="AW25" s="4">
+        <f t="shared" si="40"/>
+        <v>10488.64</v>
+      </c>
+      <c r="AX25" s="4">
+        <f t="shared" si="40"/>
+        <v>13496.239999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>36</v>
       </c>
@@ -2232,75 +3094,119 @@
         <v>1.5372881355932204</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" ref="G26" si="23">G25/G27</f>
+        <f t="shared" ref="G26:I26" si="41">G25/G27</f>
         <v>0.99406779661016953</v>
       </c>
+      <c r="H26" s="9">
+        <f t="shared" si="41"/>
+        <v>1.4497881355932203</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="41"/>
+        <v>1.5616525423728813</v>
+      </c>
       <c r="J26" s="9">
-        <f t="shared" ref="J26:K26" si="24">J25/J27</f>
+        <f t="shared" ref="J26:K26" si="42">J25/J27</f>
         <v>1.2689830508474573</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="42"/>
         <v>0.5882852292020373</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" ref="L26:N26" si="25">+L25/L27</f>
+        <f t="shared" ref="L26:N26" si="43">+L25/L27</f>
         <v>0.65984654731457804</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="43"/>
         <v>0.78942881500426254</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="43"/>
         <v>0.57337883959044367</v>
       </c>
       <c r="O26" s="1">
-        <f t="shared" ref="O26:Y26" si="26">+O25/O27</f>
+        <f t="shared" ref="O26:Y26" si="44">+O25/O27</f>
         <v>0.58177172061328786</v>
       </c>
       <c r="P26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>0.69237288135593222</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>0.95677966101694911</v>
       </c>
       <c r="R26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.0288624787775891</v>
       </c>
       <c r="S26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.0593723494486853</v>
       </c>
       <c r="T26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.298811544991511</v>
       </c>
       <c r="U26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.2641509433962264</v>
       </c>
       <c r="V26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.7795883361921099</v>
       </c>
       <c r="W26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.5364181662382177</v>
       </c>
       <c r="X26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.5274442538593482</v>
       </c>
       <c r="Y26" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="44"/>
         <v>1.7147766323024054</v>
       </c>
-    </row>
-    <row r="27" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AP26" s="1">
+        <f t="shared" ref="AP26:AQ26" si="45">+AP25/AP27</f>
+        <v>5.199329983249581</v>
+      </c>
+      <c r="AQ26" s="1">
+        <f t="shared" si="45"/>
+        <v>6.1328257191201354</v>
+      </c>
+      <c r="AR26" s="1">
+        <f>+AR25/AR27</f>
+        <v>5.052404247639581</v>
+      </c>
+      <c r="AS26" s="1">
+        <f t="shared" ref="AS26:AU26" si="46">+AS25/AS27</f>
+        <v>2.4949039003391889</v>
+      </c>
+      <c r="AT26" s="1">
+        <f t="shared" si="46"/>
+        <v>3.2606112054329373</v>
+      </c>
+      <c r="AU26" s="1">
+        <f t="shared" si="46"/>
+        <v>5.3981659202388572</v>
+      </c>
+      <c r="AV26" s="1">
+        <f>+AV25/AV27</f>
+        <v>7.0945979982842449</v>
+      </c>
+      <c r="AW26" s="1">
+        <f>+AW25/AW27</f>
+        <v>8.9979754074921345</v>
+      </c>
+      <c r="AX26" s="1">
+        <f>+AX25/AX27</f>
+        <v>11.578129825564766</v>
+      </c>
+    </row>
+    <row r="27" spans="2:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
         <v>0</v>
       </c>
@@ -2313,8 +3219,14 @@
       <c r="G27" s="5">
         <v>1180</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="H27" s="5">
+        <f>+G27</f>
+        <v>1180</v>
+      </c>
+      <c r="I27" s="5">
+        <f>+H27</f>
+        <v>1180</v>
+      </c>
       <c r="J27" s="5">
         <v>1180</v>
       </c>
@@ -2363,8 +3275,49 @@
       <c r="Y27" s="4">
         <v>1164</v>
       </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="AM27" s="4">
+        <v>1199</v>
+      </c>
+      <c r="AN27" s="4">
+        <v>1198</v>
+      </c>
+      <c r="AO27" s="4">
+        <v>1194</v>
+      </c>
+      <c r="AP27" s="4">
+        <v>1194</v>
+      </c>
+      <c r="AQ27" s="4">
+        <v>1182</v>
+      </c>
+      <c r="AR27" s="4">
+        <v>1228.504232</v>
+      </c>
+      <c r="AS27" s="4">
+        <v>1228.504232</v>
+      </c>
+      <c r="AT27" s="4">
+        <f>AVERAGE(O27:R27)</f>
+        <v>1178</v>
+      </c>
+      <c r="AU27" s="4">
+        <f>AVERAGE(S27:V27)</f>
+        <v>1172.25</v>
+      </c>
+      <c r="AV27" s="4">
+        <f>AVERAGE(W27:Z27)</f>
+        <v>1165.6666666666667</v>
+      </c>
+      <c r="AW27" s="4">
+        <f>+AV27</f>
+        <v>1165.6666666666667</v>
+      </c>
+      <c r="AX27" s="4">
+        <f>+AW27</f>
+        <v>1165.6666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>32</v>
       </c>
@@ -2373,27 +3326,27 @@
         <v>5.86019365963657E-2</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" ref="K30:P30" si="27">+K14/G14-1</f>
+        <f t="shared" ref="K30:P30" si="47">+K14/G14-1</f>
         <v>0.11483931947069936</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="47"/>
         <v>8.052181736392261E-2</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="47"/>
         <v>9.2330168005843705E-2</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="47"/>
         <v>1.0299719326383405E-2</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="47"/>
         <v>5.1575526352974466E-2</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="47"/>
         <v>4.8293089092422914E-2</v>
       </c>
       <c r="Q30" s="10">
@@ -2417,417 +3370,590 @@
         <v>9.375E-2</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" ref="V30:Y30" si="28">+V14/R14-1</f>
+        <f t="shared" ref="V30:Y30" si="48">+V14/R14-1</f>
         <v>0.10747608361875516</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="48"/>
         <v>0.12075612486009213</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="48"/>
         <v>8.9165057915058021E-2</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="48"/>
         <v>7.1546635182998752E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="T32" s="4">
-        <f>+T33-T45</f>
-        <v>8195</v>
-      </c>
-      <c r="U32" s="4">
-        <f>+U33-U45</f>
+      <c r="AM30" s="10">
+        <f t="shared" ref="AM30:AQ30" si="49">+AM14/AL14-1</f>
+        <v>6.3412201976248861E-2</v>
+      </c>
+      <c r="AN30" s="10">
+        <f t="shared" si="49"/>
+        <v>5.3152039555006247E-2</v>
+      </c>
+      <c r="AO30" s="10">
+        <f t="shared" si="49"/>
+        <v>0.11514489234256109</v>
+      </c>
+      <c r="AP30" s="10">
+        <f t="shared" si="49"/>
+        <v>2.9760824592603985E-3</v>
+      </c>
+      <c r="AQ30" s="10">
+        <f>+AQ14/AP14-1</f>
+        <v>9.4807309571196541E-3</v>
+      </c>
+      <c r="AR30" s="10">
+        <f t="shared" ref="AR30:AV30" si="50">+AR14/AQ14-1</f>
+        <v>-2.5522457611929505E-3</v>
+      </c>
+      <c r="AS30" s="10">
+        <f t="shared" si="50"/>
+        <v>7.1775115180875426E-2</v>
+      </c>
+      <c r="AT30" s="10">
+        <f t="shared" si="50"/>
+        <v>4.6407135432384505E-2</v>
+      </c>
+      <c r="AU30" s="10">
+        <f t="shared" si="50"/>
+        <v>9.513891114173112E-2</v>
+      </c>
+      <c r="AV30" s="10">
+        <f t="shared" si="50"/>
+        <v>8.1485545411985161E-2</v>
+      </c>
+      <c r="AW30" s="10">
+        <f t="shared" ref="AW30:AX30" si="51">+AW14/AV14-1</f>
+        <v>0.10278849106554611</v>
+      </c>
+      <c r="AX30" s="10">
+        <f t="shared" si="51"/>
+        <v>0.12634936211972514</v>
+      </c>
+    </row>
+    <row r="31" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="6">
+        <f>+J16/J14</f>
+        <v>0.72967622293504408</v>
+      </c>
+      <c r="K31" s="6">
+        <f t="shared" ref="K31:Z31" si="52">+K16/K14</f>
+        <v>0.70340539776741562</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.72703302803219538</v>
+      </c>
+      <c r="M31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.72756453122910258</v>
+      </c>
+      <c r="N31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73347389309190125</v>
+      </c>
+      <c r="O31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.71029293200752486</v>
+      </c>
+      <c r="P31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.71604447974583008</v>
+      </c>
+      <c r="Q31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.72778925619834711</v>
+      </c>
+      <c r="R31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73178221329868898</v>
+      </c>
+      <c r="S31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.71657754010695185</v>
+      </c>
+      <c r="T31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.72598938223938225</v>
+      </c>
+      <c r="U31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73341204250295156</v>
+      </c>
+      <c r="V31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.74032206462621308</v>
+      </c>
+      <c r="W31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73302263648468713</v>
+      </c>
+      <c r="X31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73335548908829074</v>
+      </c>
+      <c r="Y31" s="6">
+        <f t="shared" si="52"/>
+        <v>0.73501542529748787</v>
+      </c>
+      <c r="Z31" s="6">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="V32" s="4">
-        <f t="shared" ref="V32:Y32" si="29">+V33-V45</f>
+      <c r="AL31" s="6">
+        <f t="shared" ref="AL31:AV31" si="53">+AL16/AL14</f>
         <v>0</v>
       </c>
-      <c r="W32" s="4">
-        <f t="shared" si="29"/>
+      <c r="AM31" s="6">
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="X32" s="4">
-        <f t="shared" si="29"/>
+      <c r="AN31" s="6">
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="Y32" s="4">
-        <f t="shared" si="29"/>
-        <v>11835</v>
+      <c r="AO31" s="6">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="AP31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.7229962004704179</v>
+      </c>
+      <c r="AQ31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.73610065598451446</v>
+      </c>
+      <c r="AR31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.73334459386612427</v>
+      </c>
+      <c r="AS31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.72330080810112996</v>
+      </c>
+      <c r="AT31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.72185727561124102</v>
+      </c>
+      <c r="AU31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.72954705056179781</v>
+      </c>
+      <c r="AV31" s="6">
+        <f t="shared" si="53"/>
+        <v>0.73</v>
+      </c>
+      <c r="AW31" s="6">
+        <f t="shared" ref="AW31:AX31" si="54">+AW16/AW14</f>
+        <v>0.73</v>
+      </c>
+      <c r="AX31" s="6">
+        <f t="shared" si="54"/>
+        <v>0.72999999999999987</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="T33" s="4">
+        <f>+T34-T46</f>
+        <v>8195</v>
+      </c>
+      <c r="U33" s="4">
+        <f>+U34-U46</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="4">
+        <f t="shared" ref="V33:Y33" si="55">+V34-V46</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="4">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="4">
+        <f t="shared" si="55"/>
+        <v>11835</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>2</v>
       </c>
-      <c r="T33" s="4">
+      <c r="T34" s="4">
         <f>7870+3808+6109</f>
         <v>17787</v>
-      </c>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4">
-        <f>8554+1380+3964+7058</f>
-        <v>20956</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>49</v>
-      </c>
-      <c r="T34" s="4">
-        <v>6148</v>
       </c>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4">
-        <v>5778</v>
+        <f>8554+1380+3964+7058</f>
+        <v>20956</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T35" s="4">
-        <f>2531+3515</f>
-        <v>6046</v>
+        <v>6148</v>
       </c>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
       <c r="Y35" s="4">
-        <v>2777</v>
+        <v>5778</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T36" s="4">
-        <f>539+346</f>
-        <v>885</v>
+        <f>2531+3515</f>
+        <v>6046</v>
       </c>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4">
-        <f>418+317</f>
-        <v>735</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="T37" s="4">
-        <f>29777+2365</f>
-        <v>32142</v>
+        <f>539+346</f>
+        <v>885</v>
       </c>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
       <c r="Y37" s="4">
-        <f>29028+2390</f>
-        <v>31418</v>
+        <f>418+317</f>
+        <v>735</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T38" s="4">
-        <v>4255</v>
+        <f>29777+2365</f>
+        <v>32142</v>
       </c>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4">
-        <v>4396</v>
+        <f>29028+2390</f>
+        <v>31418</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T39" s="4">
-        <v>121</v>
+        <v>4255</v>
       </c>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4">
-        <v>126</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T40" s="4">
-        <v>2993</v>
+        <v>121</v>
       </c>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4">
-        <v>2210</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="T41" s="4">
+        <v>2993</v>
+      </c>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="T41" s="4">
-        <f>SUM(T33:T40)</f>
+      <c r="T42" s="4">
+        <f>SUM(T34:T41)</f>
         <v>70377</v>
       </c>
-      <c r="U41" s="4">
-        <f t="shared" ref="U41:Y41" si="30">SUM(U33:U40)</f>
+      <c r="U42" s="4">
+        <f t="shared" ref="U42:Y42" si="56">SUM(U34:U41)</f>
         <v>0</v>
       </c>
-      <c r="V41" s="4">
-        <f t="shared" si="30"/>
+      <c r="V42" s="4">
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="W41" s="4">
-        <f t="shared" si="30"/>
+      <c r="W42" s="4">
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="X41" s="4">
-        <f t="shared" si="30"/>
+      <c r="X42" s="4">
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="Y41" s="4">
-        <f t="shared" si="30"/>
+      <c r="Y42" s="4">
+        <f t="shared" si="56"/>
         <v>68396</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-    </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="T43" s="4">
-        <f>1875+20</f>
-        <v>1895</v>
-      </c>
+      <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
-      <c r="Y43" s="4">
-        <v>2074</v>
-      </c>
+      <c r="Y43" s="4"/>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="T44" s="4">
-        <f>439+818</f>
-        <v>1257</v>
+        <f>1875+20</f>
+        <v>1895</v>
       </c>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4">
-        <f>934+554</f>
-        <v>1488</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="T45" s="4">
-        <f>2271+7321</f>
-        <v>9592</v>
+        <f>439+818</f>
+        <v>1257</v>
       </c>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
       <c r="Y45" s="4">
-        <f>3032+6089</f>
-        <v>9121</v>
+        <f>934+554</f>
+        <v>1488</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T46" s="4">
-        <f>4002+850</f>
-        <v>4852</v>
+        <f>2271+7321</f>
+        <v>9592</v>
       </c>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
       <c r="Y46" s="4">
-        <f>4152+3+520</f>
-        <v>4675</v>
+        <f>3032+6089</f>
+        <v>9121</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="T47" s="4">
-        <f>2341+444</f>
-        <v>2785</v>
+        <f>4002+850</f>
+        <v>4852</v>
       </c>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
       <c r="Y47" s="4">
-        <f>170+547</f>
-        <v>717</v>
+        <f>4152+3+520</f>
+        <v>4675</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T48" s="4">
-        <f>7734+55</f>
-        <v>7789</v>
+        <f>2341+444</f>
+        <v>2785</v>
       </c>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4">
-        <f>6749+145</f>
-        <v>6894</v>
+        <f>170+547</f>
+        <v>717</v>
       </c>
     </row>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T49" s="4">
-        <v>267</v>
+        <f>7734+55</f>
+        <v>7789</v>
       </c>
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
       <c r="Y49" s="4">
-        <v>187</v>
+        <f>6749+145</f>
+        <v>6894</v>
       </c>
     </row>
     <row r="50" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T50" s="4">
-        <v>41942</v>
+        <v>267</v>
       </c>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4">
-        <v>43241</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="T51" s="4">
+        <v>41942</v>
+      </c>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4">
+        <v>43241</v>
+      </c>
+    </row>
+    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>61</v>
       </c>
-      <c r="T51" s="4">
-        <f>SUM(T43:T50)</f>
+      <c r="T52" s="4">
+        <f>SUM(T44:T51)</f>
         <v>70379</v>
       </c>
-      <c r="U51" s="4">
-        <f t="shared" ref="U51:Y51" si="31">SUM(U43:U50)</f>
+      <c r="U52" s="4">
+        <f t="shared" ref="U52:Y52" si="57">SUM(U44:U51)</f>
         <v>0</v>
       </c>
-      <c r="V51" s="4">
-        <f t="shared" si="31"/>
+      <c r="V52" s="4">
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="W51" s="4">
-        <f t="shared" si="31"/>
+      <c r="W52" s="4">
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="X51" s="4">
-        <f t="shared" si="31"/>
+      <c r="X52" s="4">
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="Y51" s="4">
-        <f t="shared" si="31"/>
+      <c r="Y52" s="4">
+        <f t="shared" si="57"/>
         <v>68397</v>
       </c>
     </row>
-    <row r="53" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+    <row r="54" spans="2:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5">
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5">
         <v>103142</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5">
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5">
         <v>104670</v>
       </c>
-      <c r="L53" s="5">
+      <c r="L54" s="5">
         <v>104988</v>
       </c>
-      <c r="M53" s="5">
+      <c r="M54" s="5">
         <v>106912</v>
       </c>
-      <c r="N53" s="5">
+      <c r="N54" s="5">
         <v>106312</v>
       </c>
-      <c r="O53" s="5">
+      <c r="O54" s="5">
         <v>105132</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P54" s="5">
         <v>105328</v>
       </c>
-      <c r="Q53" s="5">
+      <c r="Q54" s="5">
         <v>106495</v>
       </c>
-      <c r="R53" s="5">
+      <c r="R54" s="5">
         <v>107602</v>
       </c>
-      <c r="S53" s="5">
+      <c r="S54" s="5">
         <v>108133</v>
       </c>
-      <c r="T53" s="5"/>
+      <c r="T54" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2835,5 +3961,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>